--- a/KXHMONTH_2026 (decision).xlsx
+++ b/KXHMONTH_2026 (decision).xlsx
@@ -19489,7 +19489,7 @@
       <c r="K4" s="155" t="n"/>
       <c r="L4" s="68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M4" s="162" t="inlineStr">
@@ -19574,7 +19574,7 @@
       <c r="J6" s="154" t="n"/>
       <c r="K6" s="155" t="n"/>
       <c r="L6" s="71" t="n">
-        <v>0.6422</v>
+        <v>0.6314</v>
       </c>
       <c r="M6" s="162" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
       <c r="J7" s="154" t="n"/>
       <c r="K7" s="155" t="n"/>
       <c r="L7" s="71" t="n">
-        <v>0.7206</v>
+        <v>0.7027</v>
       </c>
       <c r="M7" s="162" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
       <c r="J8" s="154" t="n"/>
       <c r="K8" s="155" t="n"/>
       <c r="L8" s="71" t="n">
-        <v>0.8202</v>
+        <v>0.7921</v>
       </c>
       <c r="M8" s="162" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
       <c r="J10" s="154" t="n"/>
       <c r="K10" s="155" t="n"/>
       <c r="L10" s="80" t="n">
-        <v>0.6629</v>
+        <v>0.5656</v>
       </c>
       <c r="M10" s="162" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
       <c r="F11" s="154" t="n"/>
       <c r="G11" s="155" t="n"/>
       <c r="H11" s="80" t="n">
-        <v>0.6629</v>
+        <v>0.5656</v>
       </c>
       <c r="I11" s="162" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>0.7</v>
+        <v>0.706</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>0.5856</v>
@@ -20451,7 +20451,9 @@
           <t>Aug 03</t>
         </is>
       </c>
-      <c r="B24" s="96" t="n"/>
+      <c r="B24" s="96" t="n">
+        <v>0.6820000000000001</v>
+      </c>
       <c r="C24" s="96" t="n">
         <v>0.5709</v>
       </c>
@@ -20587,7 +20589,7 @@
       </c>
       <c r="B26" s="96" t="n"/>
       <c r="C26" s="96" t="n">
-        <v>0.6149</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="D26" s="97">
         <f>IF(OR($B26="",$C26=""),"",$B26-$C26)</f>
@@ -20620,17 +20622,17 @@
         <v/>
       </c>
       <c r="L26" s="100" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M26" s="99">
         <f>IF(OR($J26="",$L26=""),"",$L26-100*$J26)</f>
         <v/>
       </c>
       <c r="N26" s="101" t="n">
-        <v>16.57</v>
+        <v>203.19</v>
       </c>
       <c r="O26" s="101" t="n">
-        <v>1889.8</v>
+        <v>1880.61</v>
       </c>
       <c r="P26" s="102">
         <f>IF($E26="","",IF($E26&gt;0.05,"WARM dev3 — spike risk UP",IF($E26&lt;-0.05,"COLD dev3 — spike risk DOWN","")))</f>
@@ -20654,7 +20656,7 @@
       </c>
       <c r="B27" s="96" t="n"/>
       <c r="C27" s="96" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.7613</v>
       </c>
       <c r="D27" s="97">
         <f>IF(OR($B27="",$C27=""),"",$B27-$C27)</f>
@@ -20686,13 +20688,19 @@
         <f>IF($J27="","",100*(1-$J27))</f>
         <v/>
       </c>
-      <c r="L27" s="100" t="n"/>
+      <c r="L27" s="100" t="n">
+        <v>36</v>
+      </c>
       <c r="M27" s="99">
         <f>IF(OR($J27="",$L27=""),"",$L27-100*$J27)</f>
         <v/>
       </c>
-      <c r="N27" s="101" t="n"/>
-      <c r="O27" s="101" t="n"/>
+      <c r="N27" s="101" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="O27" s="101" t="n">
+        <v>1925.01</v>
+      </c>
       <c r="P27" s="102">
         <f>IF($E27="","",IF($E27&gt;0.05,"WARM dev3 — spike risk UP",IF($E27&lt;-0.05,"COLD dev3 — spike risk DOWN","")))</f>
         <v/>
@@ -20715,7 +20723,7 @@
       </c>
       <c r="B28" s="96" t="n"/>
       <c r="C28" s="96" t="n">
-        <v>0.7108</v>
+        <v>0.7431</v>
       </c>
       <c r="D28" s="97">
         <f>IF(OR($B28="",$C28=""),"",$B28-$C28)</f>
@@ -20776,7 +20784,7 @@
       </c>
       <c r="B29" s="96" t="n"/>
       <c r="C29" s="96" t="n">
-        <v>0.7298</v>
+        <v>0.7281</v>
       </c>
       <c r="D29" s="97">
         <f>IF(OR($B29="",$C29=""),"",$B29-$C29)</f>
@@ -20837,7 +20845,7 @@
       </c>
       <c r="B30" s="96" t="n"/>
       <c r="C30" s="96" t="n">
-        <v>0.7393</v>
+        <v>0.7678</v>
       </c>
       <c r="D30" s="97">
         <f>IF(OR($B30="",$C30=""),"",$B30-$C30)</f>
@@ -20898,7 +20906,7 @@
       </c>
       <c r="B31" s="96" t="n"/>
       <c r="C31" s="96" t="n">
-        <v>0.7029</v>
+        <v>0.7206</v>
       </c>
       <c r="D31" s="97">
         <f>IF(OR($B31="",$C31=""),"",$B31-$C31)</f>
@@ -20959,7 +20967,7 @@
       </c>
       <c r="B32" s="96" t="n"/>
       <c r="C32" s="96" t="n">
-        <v>0.7184</v>
+        <v>0.6784</v>
       </c>
       <c r="D32" s="97">
         <f>IF(OR($B32="",$C32=""),"",$B32-$C32)</f>
@@ -21020,7 +21028,7 @@
       </c>
       <c r="B33" s="96" t="n"/>
       <c r="C33" s="96" t="n">
-        <v>0.6796</v>
+        <v>0.6943</v>
       </c>
       <c r="D33" s="97">
         <f>IF(OR($B33="",$C33=""),"",$B33-$C33)</f>
@@ -21081,7 +21089,7 @@
       </c>
       <c r="B34" s="96" t="n"/>
       <c r="C34" s="96" t="n">
-        <v>0.7421</v>
+        <v>0.7689</v>
       </c>
       <c r="D34" s="97">
         <f>IF(OR($B34="",$C34=""),"",$B34-$C34)</f>
@@ -21142,7 +21150,7 @@
       </c>
       <c r="B35" s="96" t="n"/>
       <c r="C35" s="96" t="n">
-        <v>0.827</v>
+        <v>0.6763</v>
       </c>
       <c r="D35" s="97">
         <f>IF(OR($B35="",$C35=""),"",$B35-$C35)</f>
@@ -21203,7 +21211,7 @@
       </c>
       <c r="B36" s="96" t="n"/>
       <c r="C36" s="96" t="n">
-        <v>0.7894</v>
+        <v>0.6669</v>
       </c>
       <c r="D36" s="97">
         <f>IF(OR($B36="",$C36=""),"",$B36-$C36)</f>
@@ -21264,7 +21272,7 @@
       </c>
       <c r="B37" s="96" t="n"/>
       <c r="C37" s="96" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="D37" s="97">
         <f>IF(OR($B37="",$C37=""),"",$B37-$C37)</f>
@@ -21325,7 +21333,7 @@
       </c>
       <c r="B38" s="96" t="n"/>
       <c r="C38" s="96" t="n">
-        <v>0.6783</v>
+        <v>0.73</v>
       </c>
       <c r="D38" s="97">
         <f>IF(OR($B38="",$C38=""),"",$B38-$C38)</f>
@@ -21385,7 +21393,9 @@
         </is>
       </c>
       <c r="B39" s="96" t="n"/>
-      <c r="C39" s="96" t="n"/>
+      <c r="C39" s="96" t="n">
+        <v>0.7529</v>
+      </c>
       <c r="D39" s="97">
         <f>IF(OR($B39="",$C39=""),"",$B39-$C39)</f>
         <v/>
